--- a/api/1/clv2/xlsx/en/AidType.xlsx
+++ b/api/1/clv2/xlsx/en/AidType.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="93">
   <si>
     <t>code</t>
   </si>
@@ -281,6 +281,18 @@
   </si>
   <si>
     <t>Costs incurred in other non-ODA eligible provider countries for basic assistance to asylum seekers and refugees from developing countries, up to 12 months. The host and origin country of refugees/asylum seekers shall be specified in one of the descriptive fields of the CRS (fields 14 or 19).</t>
+  </si>
+  <si>
+    <t>J01</t>
+  </si>
+  <si>
+    <t>In-kind donation of goods</t>
+  </si>
+  <si>
+    <t>Donation of goods and materials. Includes food, equipment (including medical equipment), materials, and motor vehicles.</t>
+  </si>
+  <si>
+    <t>J</t>
   </si>
 </sst>
 </file>
@@ -612,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1057,6 +1069,23 @@
         <v>9</v>
       </c>
     </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27" t="s">
+        <v>90</v>
+      </c>
+      <c r="C27" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27" t="s">
+        <v>92</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
